--- a/boites_input.xlsx
+++ b/boites_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fofr6825\Documents\MATLAB\Adaptive-Palletizing\Adaptive-Palletizing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442E2E0D-0025-4ABE-8234-F1E5B99BE36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F2E056-0A87-45FF-9893-94D342E8E9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1D3690FE-5D9A-45E6-8524-1FA8AE5358A6}"/>
   </bookViews>
@@ -110,9 +110,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,782 +490,782 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="B2" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H2" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="B3" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H3" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="B4" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H4" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="B5" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H5" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="B6" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H6" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="B7" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H7" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="B8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H8" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H9" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="B10" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H10" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="B11" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H11" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="B12" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H12" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="B13" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H13" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="B14" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H14" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="B15" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H15" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="B16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H16" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="B17" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H17" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="B18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H18" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="B19" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H19" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="B20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H20" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H21" s="1">
+      <c r="B21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H21" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="B22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H22" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="B23" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H23" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H24" s="1">
+      <c r="B24" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H24" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H25" s="1">
+      <c r="B25" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H25" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H26" s="1">
+      <c r="B26" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H26" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H27" s="1">
+      <c r="B27" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H27" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="B28" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H28" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H29" s="1">
+      <c r="B29" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H29" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H30" s="1">
+      <c r="B30" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H30" s="2">
         <v>0.6</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="B31" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="1">
-        <v>-0.65</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H31" s="1">
+      <c r="F31" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="H31" s="2">
         <v>0.6</v>
       </c>
     </row>
